--- a/assets/TX-FL Business Listings.R0.xlsx
+++ b/assets/TX-FL Business Listings.R0.xlsx
@@ -1,25 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jared\source\repos\avtopia\data_sync_desktop\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F61CFB-9621-4E7C-8C93-3E2AE4CDBF37}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6CB47A6-1D57-47FB-A177-0EF048673B4B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3435" yWindow="1335" windowWidth="21600" windowHeight="13230" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BetaData" sheetId="1" r:id="rId1"/>
     <sheet name="BetaDataResults" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BetaData!$H$1:$H$496</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -17363,6 +17375,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="H1:H496" xr:uid="{A0FBB3C1-9F9E-49FC-BDAA-E8D8CDA613E3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
